--- a/B3_mask輔助對照_11.xlsx
+++ b/B3_mask輔助對照_11.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="逐顆牙對照" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="三法比較" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="視覺化圖例" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="視覺化圖例" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y55"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,12 +430,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>AB長度_原始預測_letterbox px</t>
+          <t>原圖寬</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>AB長度_原始預測_原圖px</t>
+          <t>原圖高</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -456,110 +455,101 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>GT格式</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>兩法選取一致</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>mask_IoU_vs_GT框</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>次佳mask_IoU</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>A點到mask邊界px</t>
-        </is>
-      </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>B點到mask邊界px</t>
+          <t>長軸解釋比</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>長軸解釋比</t>
+          <t>牙位</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>AB長度_長軸投影_letterbox px</t>
+          <t>方向依據</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>寬度法方向一致</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>兩端寬度比</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>AB長度_mask幾何_letterbox px</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>AB長度_長軸投影_原圖px</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>AB長度_mask幾何_原圖px</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>幾何端點誤差_A側px</t>
-        </is>
-      </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>幾何端點誤差_B側px</t>
+          <t>冠寬_letterbox px</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>預測點誤差_A側px</t>
+          <t>冠寬_原圖px</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>預測點誤差_B側px</t>
+          <t>冠寬位置_距A端比例</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>長寬比_mask幾何÷冠寬</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>QC備註</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>建議人工複查</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>真實AB像素長度_letterbox px</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>真實AB像素長度_原圖px</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>001_jpg.rf.4c9b567ff4deaebc95dfe818620028ba.jpg</t>
+          <t>001_jpg.rf.f66116916f1034ff42d3ca622244a7a1.jpg</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.797011</v>
       </c>
-      <c r="C2" t="n">
-        <v>374.245</v>
-      </c>
-      <c r="D2" t="n">
-        <v>298.2773</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -575,80 +565,75 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0.805</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J2" t="n">
-        <v>0.021</v>
+        <v>0.973</v>
       </c>
       <c r="K2" t="n">
-        <v>13.75</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-6.45</v>
+        <v>0.795</v>
       </c>
       <c r="M2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="N2" t="n">
-        <v>373.8843</v>
-      </c>
-      <c r="O2" t="n">
+        <v>22</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="Q2" t="n">
         <v>385.491</v>
       </c>
-      <c r="P2" t="n">
-        <v>297.9899</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>307.2406</v>
       </c>
-      <c r="R2" t="n">
-        <v>14.35</v>
-      </c>
       <c r="S2" t="n">
-        <v>15.56</v>
+        <v>118</v>
       </c>
       <c r="T2" t="n">
-        <v>14.97</v>
+        <v>94.04730000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X2" t="n">
-        <v>383.9851</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>481.7814</v>
+        <v>0.113</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.2669</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>002_jpg.rf.e7a3fcb45d83e3a2dd6afbe241bd1d73.jpg</t>
+          <t>002_jpg.rf.9963a010c88f0c1cc16485557aa5bbe6.jpg</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C3" t="n">
-        <v>401.4351</v>
-      </c>
-      <c r="D3" t="n">
-        <v>214.0986</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>✅</t>
@@ -664,80 +649,75 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.8090000000000001</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J3" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>10.18</v>
-      </c>
       <c r="L3" t="n">
-        <v>-33.55</v>
+        <v>0.719</v>
       </c>
       <c r="M3" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="N3" t="n">
-        <v>399.4448</v>
-      </c>
-      <c r="O3" t="n">
-        <v>379.6752</v>
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P3" t="n">
-        <v>213.0371</v>
+        <v>2.496</v>
       </c>
       <c r="Q3" t="n">
-        <v>202.4933</v>
+        <v>379.4327</v>
       </c>
       <c r="R3" t="n">
-        <v>22.85</v>
+        <v>202.364</v>
       </c>
       <c r="S3" t="n">
-        <v>45.58</v>
+        <v>160</v>
       </c>
       <c r="T3" t="n">
-        <v>14.16</v>
+        <v>85.33329999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>B點在mask外、牙形不夠細長、端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X3" t="n">
-        <v>371.4222</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>696.4171</v>
+        <v>0.117</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.3715</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>003_jpg.rf.1f6d62636a99328020108bb78ef3c835.jpg</t>
+          <t>003_jpg.rf.e51ad05d7f902b25c75f3306c011afb7.jpg</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C4" t="n">
-        <v>506.5941</v>
-      </c>
-      <c r="D4" t="n">
-        <v>270.1834</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>✅</t>
@@ -753,80 +733,75 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.877</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J4" t="n">
-        <v>0.021</v>
+        <v>0.971</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.22</v>
+        <v>0.032</v>
       </c>
       <c r="L4" t="n">
-        <v>-35.02</v>
+        <v>0.743</v>
       </c>
       <c r="M4" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="N4" t="n">
-        <v>506.4906</v>
-      </c>
-      <c r="O4" t="n">
-        <v>462.3287</v>
+        <v>21</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P4" t="n">
-        <v>270.1282</v>
+        <v>2.589</v>
       </c>
       <c r="Q4" t="n">
-        <v>246.5751</v>
+        <v>462.3284</v>
       </c>
       <c r="R4" t="n">
-        <v>5.96</v>
+        <v>246.575</v>
       </c>
       <c r="S4" t="n">
-        <v>31.67</v>
+        <v>160</v>
       </c>
       <c r="T4" t="n">
-        <v>13.11</v>
+        <v>85.33329999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>A點在mask外、B點在mask外、牙形不夠細長</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X4" t="n">
-        <v>480.5272</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>900.9891</v>
+        <v>0.142</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.8896</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>004_jpg.rf.4013d1526ae79399b0311b45cce6dc49.jpg</t>
+          <t>004_jpg.rf.91185a83cc0c80eb5944863f195e0be0.jpg</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C5" t="n">
-        <v>361.3462</v>
-      </c>
-      <c r="D5" t="n">
-        <v>192.7178</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>✅</t>
@@ -842,76 +817,79 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.752</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J5" t="n">
-        <v>0.221</v>
+        <v>0.965</v>
       </c>
       <c r="K5" t="n">
-        <v>10.55</v>
+        <v>0.237</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.82</v>
+        <v>0.772</v>
       </c>
       <c r="M5" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="N5" t="n">
-        <v>360.4119</v>
-      </c>
-      <c r="O5" t="n">
-        <v>367.8579</v>
+        <v>31</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P5" t="n">
-        <v>192.2196</v>
+        <v>2.275</v>
       </c>
       <c r="Q5" t="n">
-        <v>196.1907</v>
+        <v>367.8574</v>
       </c>
       <c r="R5" t="n">
-        <v>4.52</v>
+        <v>196.1905</v>
       </c>
       <c r="S5" t="n">
-        <v>36.78</v>
+        <v>103</v>
       </c>
       <c r="T5" t="n">
-        <v>8.57</v>
+        <v>54.9333</v>
       </c>
       <c r="U5" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>0.056</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.5714</v>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
-        <v>365.0521</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>684.4731</v>
+          <t>兩法選到不同mask、冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>⚠️是</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>005_jpg.rf.db41c76a1a0f67c029e07def41fa7e71.jpg</t>
+          <t>005_jpg.rf.d6bfd25b1c387295bb0a4f9324b63b01.jpg</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C6" t="n">
-        <v>370.3064</v>
-      </c>
-      <c r="D6" t="n">
-        <v>197.4966</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>✅</t>
@@ -927,80 +905,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6830000000000001</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J6" t="n">
-        <v>0.108</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>14.18</v>
+        <v>0.092</v>
       </c>
       <c r="L6" t="n">
-        <v>-18.29</v>
+        <v>0.774</v>
       </c>
       <c r="M6" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="N6" t="n">
-        <v>370.0556</v>
-      </c>
-      <c r="O6" t="n">
+        <v>22</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>2.702</v>
+      </c>
+      <c r="Q6" t="n">
         <v>400.5039</v>
       </c>
-      <c r="P6" t="n">
-        <v>197.3628</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>213.602</v>
       </c>
-      <c r="R6" t="n">
-        <v>6.58</v>
-      </c>
       <c r="S6" t="n">
-        <v>21.71</v>
+        <v>135.5</v>
       </c>
       <c r="T6" t="n">
-        <v>19.98</v>
+        <v>72.2666</v>
       </c>
       <c r="U6" t="n">
-        <v>30.75</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X6" t="n">
-        <v>402.6114</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>754.8968</v>
+        <v>0.171</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.9557</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>006_jpg.rf.d226f3637e96179b1db115d31f983def.jpg</t>
+          <t>006_jpg.rf.8f9677e435d9bab806aec41abe9c509c.jpg</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C7" t="n">
-        <v>461.0285</v>
-      </c>
-      <c r="D7" t="n">
-        <v>245.8817</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1016,80 +989,75 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.875</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J7" t="n">
-        <v>0.026</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>9.93</v>
+        <v>0.001</v>
       </c>
       <c r="L7" t="n">
-        <v>-10.6</v>
+        <v>0.747</v>
       </c>
       <c r="M7" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="N7" t="n">
-        <v>461.0283</v>
-      </c>
-      <c r="O7" t="n">
-        <v>465.6629</v>
+        <v>21</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P7" t="n">
-        <v>245.8816</v>
+        <v>2.709</v>
       </c>
       <c r="Q7" t="n">
-        <v>248.3534</v>
+        <v>465.6388</v>
       </c>
       <c r="R7" t="n">
-        <v>16.31</v>
+        <v>248.3405</v>
       </c>
       <c r="S7" t="n">
-        <v>20.14</v>
+        <v>160</v>
       </c>
       <c r="T7" t="n">
-        <v>5.4</v>
+        <v>85.33329999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>B點在mask外、牙形不夠細長、端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
-        <v>460.8032</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>864.0065</v>
+        <v>0.213</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.9102</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>007_jpg.rf.700d0bf10fa8fd648835e0074572e5d8.jpg</t>
+          <t>007_jpg.rf.28f6235ca85bfe67778bf72f55c5c953.jpg</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C8" t="n">
-        <v>502.0849</v>
-      </c>
-      <c r="D8" t="n">
-        <v>267.7784</v>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1105,80 +1073,75 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.765</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J8" t="n">
-        <v>0.063</v>
+        <v>0.991</v>
       </c>
       <c r="K8" t="n">
-        <v>7.57</v>
+        <v>0.012</v>
       </c>
       <c r="L8" t="n">
-        <v>-37.09</v>
+        <v>0.792</v>
       </c>
       <c r="M8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="N8" t="n">
-        <v>499.8561</v>
-      </c>
-      <c r="O8" t="n">
-        <v>472.5535</v>
+        <v>11</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P8" t="n">
-        <v>266.5898</v>
+        <v>2.057</v>
       </c>
       <c r="Q8" t="n">
-        <v>252.0284</v>
+        <v>476.281</v>
       </c>
       <c r="R8" t="n">
-        <v>17.97</v>
+        <v>254.0164</v>
       </c>
       <c r="S8" t="n">
-        <v>34.97</v>
+        <v>137</v>
       </c>
       <c r="T8" t="n">
-        <v>34.57</v>
+        <v>73.06659999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X8" t="n">
-        <v>485.6909</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>910.671</v>
+        <v>0.125</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.4765</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>008_jpg.rf.5812b75fe38ce91b0ecc6190e59be8c3.jpg</t>
+          <t>008_jpg.rf.6e25bbbe74b05332cd98a16ebc2d06c0.jpg</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.810127</v>
       </c>
-      <c r="C9" t="n">
-        <v>341.3758</v>
-      </c>
-      <c r="D9" t="n">
-        <v>276.5577</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1194,76 +1157,75 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.721</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J9" t="n">
-        <v>0.191</v>
+        <v>0.968</v>
       </c>
       <c r="K9" t="n">
-        <v>19.94</v>
+        <v>0.122</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.53</v>
+        <v>0.77</v>
       </c>
       <c r="M9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="N9" t="n">
-        <v>340.8996</v>
-      </c>
-      <c r="O9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>2.229</v>
+      </c>
+      <c r="Q9" t="n">
         <v>363.598</v>
       </c>
-      <c r="P9" t="n">
-        <v>276.172</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>294.5606</v>
       </c>
-      <c r="R9" t="n">
-        <v>5.28</v>
-      </c>
       <c r="S9" t="n">
-        <v>23.26</v>
+        <v>113</v>
       </c>
       <c r="T9" t="n">
-        <v>17.87</v>
+        <v>91.5444</v>
       </c>
       <c r="U9" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr">
+        <v>0.111</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.2177</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
         <is>
           <t>否</t>
         </is>
-      </c>
-      <c r="X9" t="n">
-        <v>363.171</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>448.289</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>009_jpg.rf.8bab93b7d56749aa98648bdd1ca7afdb.jpg</t>
+          <t>009_jpg.rf.5810c0777bc3544fa8a8c4a2eec91372.jpg</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C10" t="n">
-        <v>388.326</v>
-      </c>
-      <c r="D10" t="n">
-        <v>103.5537</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1279,76 +1241,75 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.895</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J10" t="n">
-        <v>0.053</v>
+        <v>0.985</v>
       </c>
       <c r="K10" t="n">
-        <v>13.24</v>
+        <v>0.034</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.99</v>
+        <v>0.772</v>
       </c>
       <c r="M10" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="N10" t="n">
-        <v>387.8375</v>
-      </c>
-      <c r="O10" t="n">
-        <v>406.3388</v>
+        <v>12</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P10" t="n">
-        <v>103.4235</v>
+        <v>1.937</v>
       </c>
       <c r="Q10" t="n">
-        <v>108.3572</v>
+        <v>406.3358</v>
       </c>
       <c r="R10" t="n">
-        <v>5.5</v>
+        <v>108.3564</v>
       </c>
       <c r="S10" t="n">
-        <v>8.220000000000001</v>
+        <v>127</v>
       </c>
       <c r="T10" t="n">
-        <v>19.81</v>
+        <v>33.8667</v>
       </c>
       <c r="U10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr">
+        <v>0.142</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.1995</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
         <is>
           <t>否</t>
         </is>
-      </c>
-      <c r="X10" t="n">
-        <v>404.474</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1516.7756</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>010_jpg.rf.548a6fc07e0dd15ce1fb1c2efc5af9fa.jpg</t>
+          <t>010_jpg.rf.9cbc38a1e354038183129ed3ce5be3bd.jpg</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.777643</v>
       </c>
-      <c r="C11" t="n">
-        <v>289.9418</v>
-      </c>
-      <c r="D11" t="n">
-        <v>225.4712</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1364,76 +1325,79 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.769</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J11" t="n">
-        <v>0.096</v>
+        <v>0.979</v>
       </c>
       <c r="K11" t="n">
-        <v>2.44</v>
+        <v>0.031</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08</v>
+        <v>0.777</v>
       </c>
       <c r="M11" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="N11" t="n">
-        <v>289.9218</v>
-      </c>
-      <c r="O11" t="n">
+        <v>41</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="Q11" t="n">
         <v>294.9144</v>
       </c>
-      <c r="P11" t="n">
-        <v>225.4557</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>229.3381</v>
       </c>
-      <c r="R11" t="n">
-        <v>10.93</v>
-      </c>
       <c r="S11" t="n">
-        <v>13.7</v>
+        <v>92</v>
       </c>
       <c r="T11" t="n">
-        <v>7.03</v>
+        <v>71.5432</v>
       </c>
       <c r="U11" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.2056</v>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X11" t="n">
-        <v>288.8845</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>371.4873</v>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>⚠️是</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>011_jpg.rf.31dfe6cf21e941713e13d48e451b5b34.jpg</t>
+          <t>011_jpg.rf.93e0abfd1c8ba679d6229582d68e3ebd.jpg</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C12" t="n">
-        <v>452.2552</v>
-      </c>
-      <c r="D12" t="n">
-        <v>241.2026</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1449,80 +1413,75 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.728</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J12" t="n">
-        <v>0.11</v>
+        <v>0.946</v>
       </c>
       <c r="K12" t="n">
-        <v>7.27</v>
+        <v>0.108</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.06</v>
+        <v>0.759</v>
       </c>
       <c r="M12" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="N12" t="n">
-        <v>452.2551</v>
-      </c>
-      <c r="O12" t="n">
-        <v>462.6199</v>
+        <v>21</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P12" t="n">
-        <v>241.2026</v>
+        <v>2.275</v>
       </c>
       <c r="Q12" t="n">
-        <v>246.7305</v>
+        <v>462.622</v>
       </c>
       <c r="R12" t="n">
-        <v>17.02</v>
+        <v>246.7316</v>
       </c>
       <c r="S12" t="n">
-        <v>28.08</v>
+        <v>157</v>
       </c>
       <c r="T12" t="n">
-        <v>13.47</v>
+        <v>83.7333</v>
       </c>
       <c r="U12" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X12" t="n">
-        <v>473.0808</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>887.0271</v>
+        <v>0.111</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.9466</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>012_jpg.rf.1c49f445f9a076103a044e4d7ec4cbba.jpg</t>
+          <t>012_jpg.rf.e1e691535b634f6242b0126913c1555e.jpg</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C13" t="n">
-        <v>375.9922</v>
-      </c>
-      <c r="D13" t="n">
-        <v>200.5291</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1538,80 +1497,79 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.779</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J13" t="n">
-        <v>0.163</v>
+        <v>0.948</v>
       </c>
       <c r="K13" t="n">
-        <v>26.33</v>
+        <v>0.115</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.59</v>
+        <v>0.718</v>
       </c>
       <c r="M13" t="n">
-        <v>0.717</v>
-      </c>
-      <c r="N13" t="n">
-        <v>374.6311</v>
-      </c>
-      <c r="O13" t="n">
-        <v>407.107</v>
+        <v>22</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P13" t="n">
-        <v>199.8031</v>
+        <v>2.386</v>
       </c>
       <c r="Q13" t="n">
-        <v>217.1236</v>
+        <v>407.1404</v>
       </c>
       <c r="R13" t="n">
-        <v>6.29</v>
+        <v>217.1414</v>
       </c>
       <c r="S13" t="n">
-        <v>42.74</v>
+        <v>136</v>
       </c>
       <c r="T13" t="n">
-        <v>26.73</v>
+        <v>72.5333</v>
       </c>
       <c r="U13" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>牙形不夠細長</t>
-        </is>
+        <v>0.136</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.9937</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X13" t="n">
-        <v>416.9901</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>781.8569</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>013_jpg.rf.5aa0c8322ac4e403fc96ddf0b299a532.jpg</t>
+          <t>013_jpg.rf.74670a19a61e8d2ab4d6df93a721d0bf.jpg</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C14" t="n">
-        <v>378.4144</v>
-      </c>
-      <c r="D14" t="n">
-        <v>201.8209</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1627,76 +1585,75 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.795</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J14" t="n">
-        <v>0.073</v>
+        <v>0.952</v>
       </c>
       <c r="K14" t="n">
-        <v>29.93</v>
+        <v>0.001</v>
       </c>
       <c r="L14" t="n">
-        <v>13.12</v>
+        <v>0.767</v>
       </c>
       <c r="M14" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="N14" t="n">
-        <v>378.2515</v>
-      </c>
-      <c r="O14" t="n">
-        <v>427.9653</v>
+        <v>11</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P14" t="n">
-        <v>201.734</v>
+        <v>1.905</v>
       </c>
       <c r="Q14" t="n">
-        <v>228.248</v>
+        <v>428.0421</v>
       </c>
       <c r="R14" t="n">
-        <v>9.85</v>
+        <v>228.289</v>
       </c>
       <c r="S14" t="n">
-        <v>7.04</v>
+        <v>138</v>
       </c>
       <c r="T14" t="n">
-        <v>26.62</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr">
+        <v>0.13</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.1018</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
-      </c>
-      <c r="X14" t="n">
-        <v>421.4061</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>790.1369</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>014_jpg.rf.3c9e80b37f0a897edf939f5b2a539ad8.jpg</t>
+          <t>014_jpg.rf.054fe3761f03a25fffe36bdaa7ab23e2.jpg</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C15" t="n">
-        <v>339.8632</v>
-      </c>
-      <c r="D15" t="n">
-        <v>181.2602</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1712,76 +1669,75 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.788</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J15" t="n">
-        <v>0.211</v>
+        <v>0.979</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>0.129</v>
       </c>
       <c r="L15" t="n">
-        <v>21.54</v>
+        <v>0.77</v>
       </c>
       <c r="M15" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="N15" t="n">
-        <v>339.1709</v>
-      </c>
-      <c r="O15" t="n">
+        <v>31</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="Q15" t="n">
         <v>369.2678</v>
       </c>
-      <c r="P15" t="n">
-        <v>180.891</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>196.9427</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.06</v>
-      </c>
       <c r="S15" t="n">
-        <v>24.96</v>
+        <v>93</v>
       </c>
       <c r="T15" t="n">
-        <v>6.54</v>
+        <v>49.6</v>
       </c>
       <c r="U15" t="n">
-        <v>26.41</v>
-      </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
+        <v>0.332</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.9706</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
         <is>
           <t>否</t>
         </is>
-      </c>
-      <c r="X15" t="n">
-        <v>368.5682</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>691.0658</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>015_jpg.rf.94b4a7961d4eac445d4907eb273a8c9c.jpg</t>
+          <t>015_jpg.rf.695fde2697827038b691a9db68c2ea6d.jpg</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C16" t="n">
-        <v>380.3762</v>
-      </c>
-      <c r="D16" t="n">
-        <v>202.8672</v>
-      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1797,76 +1753,75 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.79</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J16" t="n">
-        <v>0.065</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.33</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.32</v>
+        <v>0.819</v>
       </c>
       <c r="M16" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="N16" t="n">
-        <v>380.3502</v>
-      </c>
-      <c r="O16" t="n">
-        <v>390.9824</v>
+        <v>31</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P16" t="n">
-        <v>202.8533</v>
+        <v>1.756</v>
       </c>
       <c r="Q16" t="n">
-        <v>208.5238</v>
+        <v>390.983</v>
       </c>
       <c r="R16" t="n">
-        <v>2.54</v>
+        <v>208.5242</v>
       </c>
       <c r="S16" t="n">
-        <v>14.4</v>
+        <v>87</v>
       </c>
       <c r="T16" t="n">
-        <v>4.35</v>
+        <v>46.4</v>
       </c>
       <c r="U16" t="n">
-        <v>17.49</v>
-      </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr">
+        <v>0.225</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.4941</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
-      </c>
-      <c r="X16" t="n">
-        <v>389.0375</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>729.4458</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>016_jpg.rf.7ab63b1fd0e68335acee897bc3b0a865.jpg</t>
+          <t>016_jpg.rf.75bb53bb5f2a011d156abea4e002179b.jpg</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C17" t="n">
-        <v>345.1232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>92.033</v>
-      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1882,76 +1837,75 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.618</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J17" t="n">
-        <v>0.203</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>1.88</v>
+        <v>0.041</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="N17" t="n">
-        <v>344.457</v>
-      </c>
-      <c r="O17" t="n">
+        <v>31</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1.971</v>
+      </c>
+      <c r="Q17" t="n">
         <v>351.6249</v>
       </c>
-      <c r="P17" t="n">
-        <v>91.8553</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>93.7668</v>
       </c>
-      <c r="R17" t="n">
-        <v>10.79</v>
-      </c>
       <c r="S17" t="n">
-        <v>26.38</v>
+        <v>85</v>
       </c>
       <c r="T17" t="n">
-        <v>9.69</v>
+        <v>22.6667</v>
       </c>
       <c r="U17" t="n">
-        <v>14</v>
-      </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr">
+        <v>0.133</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.1368</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
-      </c>
-      <c r="X17" t="n">
-        <v>351.2872</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1317.3254</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>017_jpg.rf.f41244d846f5acefd512d3fe33b1f7c7.jpg</t>
+          <t>017_jpg.rf.ad10c8b2d6a91298ac0054c6c5a26048.jpg</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C18" t="n">
-        <v>441.2503</v>
-      </c>
-      <c r="D18" t="n">
-        <v>117.6669</v>
-      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1967,80 +1921,75 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.789</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.968</v>
       </c>
       <c r="K18" t="n">
-        <v>13.47</v>
+        <v>0.105</v>
       </c>
       <c r="L18" t="n">
-        <v>4.77</v>
+        <v>0.76</v>
       </c>
       <c r="M18" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="N18" t="n">
-        <v>441.139</v>
-      </c>
-      <c r="O18" t="n">
-        <v>460.6032</v>
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P18" t="n">
-        <v>117.6372</v>
+        <v>2.129</v>
       </c>
       <c r="Q18" t="n">
-        <v>122.8277</v>
+        <v>460.6025</v>
       </c>
       <c r="R18" t="n">
-        <v>29.32</v>
+        <v>122.8275</v>
       </c>
       <c r="S18" t="n">
-        <v>22.29</v>
+        <v>154</v>
       </c>
       <c r="T18" t="n">
-        <v>32.77</v>
+        <v>41.0667</v>
       </c>
       <c r="U18" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X18" t="n">
-        <v>468.3791</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1756.4194</v>
+        <v>0.127</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.9909</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>018_jpg.rf.22c1355b4bd4dc78157bf7cb3b88bd48.jpg</t>
+          <t>018_jpg.rf.91c3434693356f69dcfb4ff1391ae50a.jpg</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C19" t="n">
-        <v>389.7565</v>
-      </c>
-      <c r="D19" t="n">
-        <v>207.87</v>
-      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2056,80 +2005,75 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.789</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J19" t="n">
-        <v>0.158</v>
+        <v>0.985</v>
       </c>
       <c r="K19" t="n">
-        <v>22.36</v>
+        <v>0.152</v>
       </c>
       <c r="L19" t="n">
-        <v>-10.86</v>
+        <v>0.785</v>
       </c>
       <c r="M19" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="N19" t="n">
-        <v>389.4768</v>
-      </c>
-      <c r="O19" t="n">
-        <v>421.9962</v>
+        <v>22</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P19" t="n">
-        <v>207.7208</v>
+        <v>1.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>225.0645</v>
+        <v>421.9001</v>
       </c>
       <c r="R19" t="n">
-        <v>14.37</v>
+        <v>225.0133</v>
       </c>
       <c r="S19" t="n">
-        <v>13.22</v>
+        <v>129</v>
       </c>
       <c r="T19" t="n">
-        <v>40.66</v>
+        <v>68.8</v>
       </c>
       <c r="U19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>B點在mask外、端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X19" t="n">
-        <v>418.4228</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>784.5432</v>
+        <v>0.132</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3.2705</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>019_jpg.rf.5b1215807086f746eeb6c3f30bedcbee.jpg</t>
+          <t>019_jpg.rf.02669a2475da43f4dd5937f69b679539.jpg</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C20" t="n">
-        <v>475.7593</v>
-      </c>
-      <c r="D20" t="n">
-        <v>253.7381</v>
-      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2145,80 +2089,79 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>0.865</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J20" t="n">
-        <v>0.187</v>
+        <v>0.98</v>
       </c>
       <c r="K20" t="n">
-        <v>10.71</v>
+        <v>0.18</v>
       </c>
       <c r="L20" t="n">
-        <v>-10.54</v>
+        <v>0.785</v>
       </c>
       <c r="M20" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="N20" t="n">
-        <v>475.5373</v>
-      </c>
-      <c r="O20" t="n">
-        <v>482.2599</v>
+        <v>11</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P20" t="n">
-        <v>253.6197</v>
+        <v>2.508</v>
       </c>
       <c r="Q20" t="n">
-        <v>257.2051</v>
+        <v>482.2692</v>
       </c>
       <c r="R20" t="n">
-        <v>10.44</v>
+        <v>257.2101</v>
       </c>
       <c r="S20" t="n">
-        <v>2.24</v>
+        <v>148</v>
       </c>
       <c r="T20" t="n">
-        <v>17.09</v>
+        <v>78.9333</v>
       </c>
       <c r="U20" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
+        <v>0.158</v>
+      </c>
+      <c r="V20" t="n">
+        <v>3.2586</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X20" t="n">
-        <v>473.2923</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>887.4236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>020_jpg.rf.6f3df25507befe53cc2fe1e6839d320a.jpg</t>
+          <t>020_jpg.rf.8aea54730f3eaefab1a23f121a8cdde5.jpg</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0.813215</v>
       </c>
-      <c r="C21" t="n">
-        <v>314.3661</v>
-      </c>
-      <c r="D21" t="n">
-        <v>255.6472</v>
-      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2234,80 +2177,79 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>0.845</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J21" t="n">
-        <v>0.016</v>
+        <v>0.984</v>
       </c>
       <c r="K21" t="n">
-        <v>6.88</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5.98</v>
+        <v>0.72</v>
       </c>
       <c r="M21" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="N21" t="n">
-        <v>314.3585</v>
-      </c>
-      <c r="O21" t="n">
-        <v>328.9588</v>
+        <v>11</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P21" t="n">
-        <v>255.641</v>
+        <v>1.926</v>
       </c>
       <c r="Q21" t="n">
-        <v>267.5142</v>
+        <v>328.9585</v>
       </c>
       <c r="R21" t="n">
-        <v>5.23</v>
+        <v>267.514</v>
       </c>
       <c r="S21" t="n">
-        <v>12.47</v>
+        <v>131</v>
       </c>
       <c r="T21" t="n">
-        <v>8.800000000000001</v>
+        <v>106.5312</v>
       </c>
       <c r="U21" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>牙形不夠細長</t>
-        </is>
+        <v>0.105</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.5111</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X21" t="n">
-        <v>333.3879</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>409.9628</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>021_jpg.rf.8b63d0945baeef56e60cbc002150e4bb.jpg</t>
+          <t>021_jpg.rf.0e141b251ddd95981fa303ac34074643.jpg</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C22" t="n">
-        <v>374.6458</v>
-      </c>
-      <c r="D22" t="n">
-        <v>199.8109</v>
-      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2323,80 +2265,75 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0.828</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J22" t="n">
-        <v>0.046</v>
+        <v>0.962</v>
       </c>
       <c r="K22" t="n">
-        <v>14.61</v>
+        <v>0.023</v>
       </c>
       <c r="L22" t="n">
-        <v>-10.14</v>
+        <v>0.756</v>
       </c>
       <c r="M22" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="N22" t="n">
-        <v>372.6404</v>
-      </c>
-      <c r="O22" t="n">
-        <v>387.2686</v>
+        <v>12</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P22" t="n">
-        <v>198.7414</v>
+        <v>2.094</v>
       </c>
       <c r="Q22" t="n">
-        <v>206.5431</v>
+        <v>387.2124</v>
       </c>
       <c r="R22" t="n">
-        <v>8.93</v>
+        <v>206.5131</v>
       </c>
       <c r="S22" t="n">
-        <v>14.29</v>
+        <v>129</v>
       </c>
       <c r="T22" t="n">
-        <v>26.81</v>
+        <v>68.8</v>
       </c>
       <c r="U22" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X22" t="n">
-        <v>392.9243</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>736.7335</v>
+        <v>0.161</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.0016</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>022_jpg.rf.116af67b6e3794e3f8ed2f5d51cca8a1.jpg</t>
+          <t>022_jpg.rf.d81f9540b892ea7ac37449e2e58cd185.jpg</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C23" t="n">
-        <v>420.3014</v>
-      </c>
-      <c r="D23" t="n">
-        <v>224.1606</v>
-      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2412,80 +2349,79 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>0.852</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J23" t="n">
-        <v>0.107</v>
+        <v>0.95</v>
       </c>
       <c r="K23" t="n">
-        <v>18.82</v>
+        <v>0.121</v>
       </c>
       <c r="L23" t="n">
-        <v>-21.15</v>
+        <v>0.753</v>
       </c>
       <c r="M23" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="N23" t="n">
-        <v>420.2247</v>
-      </c>
-      <c r="O23" t="n">
-        <v>420.4339</v>
+        <v>11</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P23" t="n">
-        <v>224.1197</v>
+        <v>2.174</v>
       </c>
       <c r="Q23" t="n">
-        <v>224.2312</v>
+        <v>420.4336</v>
       </c>
       <c r="R23" t="n">
-        <v>12.68</v>
+        <v>224.2311</v>
       </c>
       <c r="S23" t="n">
-        <v>18.69</v>
+        <v>148</v>
       </c>
       <c r="T23" t="n">
-        <v>13.68</v>
+        <v>78.9333</v>
       </c>
       <c r="U23" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>B點在mask外、端點誤差抵銷(長度假準)</t>
-        </is>
+        <v>0.118</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.8408</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X23" t="n">
-        <v>430.9025</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>807.9426999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>023_jpg.rf.c81eb814a1c67711193aa6d0ef2ba449.jpg</t>
+          <t>023_jpg.rf.a75c697708b75f0450bb502534659862.jpg</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C24" t="n">
-        <v>388.0057</v>
-      </c>
-      <c r="D24" t="n">
-        <v>206.9363</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2501,80 +2437,79 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>0.895</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J24" t="n">
-        <v>0.022</v>
+        <v>0.966</v>
       </c>
       <c r="K24" t="n">
-        <v>5.25</v>
+        <v>0.01</v>
       </c>
       <c r="L24" t="n">
-        <v>-25.66</v>
+        <v>0.695</v>
       </c>
       <c r="M24" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="N24" t="n">
-        <v>387.0534</v>
-      </c>
-      <c r="O24" t="n">
-        <v>372.3785</v>
+        <v>21</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P24" t="n">
-        <v>206.4284</v>
+        <v>2.492</v>
       </c>
       <c r="Q24" t="n">
-        <v>198.6017</v>
+        <v>372.3805</v>
       </c>
       <c r="R24" t="n">
-        <v>13.35</v>
+        <v>198.6028</v>
       </c>
       <c r="S24" t="n">
-        <v>21.08</v>
+        <v>161</v>
       </c>
       <c r="T24" t="n">
-        <v>6.05</v>
+        <v>85.86660000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>25.05</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>B點在mask外、牙形不夠細長、端點誤差抵銷(長度假準)</t>
-        </is>
+        <v>0.138</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.3129</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
+          <t>牙形不夠細長</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X24" t="n">
-        <v>361.1062</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>677.0744999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>024_jpg.rf.32a9c8afc84e54eb0a5df0b4c0ce394c.jpg</t>
+          <t>024_jpg.rf.b906eee89bff6be48d0b1f393563afe5.jpg</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C25" t="n">
-        <v>340.4863</v>
-      </c>
-      <c r="D25" t="n">
-        <v>181.5926</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2590,80 +2525,79 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>0.753</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J25" t="n">
-        <v>0.092</v>
+        <v>0.97</v>
       </c>
       <c r="K25" t="n">
-        <v>13.46</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>11.57</v>
+        <v>0.736</v>
       </c>
       <c r="M25" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="N25" t="n">
-        <v>340.1795</v>
-      </c>
-      <c r="O25" t="n">
-        <v>367.0181</v>
+        <v>22</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P25" t="n">
-        <v>181.4289</v>
+        <v>1.814</v>
       </c>
       <c r="Q25" t="n">
-        <v>195.7429</v>
+        <v>367.0185</v>
       </c>
       <c r="R25" t="n">
-        <v>12.8</v>
+        <v>195.7431</v>
       </c>
       <c r="S25" t="n">
-        <v>29.23</v>
+        <v>136</v>
       </c>
       <c r="T25" t="n">
-        <v>18.98</v>
+        <v>72.5333</v>
       </c>
       <c r="U25" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>牙形不夠細長、端點誤差抵銷(長度假準)</t>
-        </is>
+        <v>0.192</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.6987</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X25" t="n">
-        <v>362.2152</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>679.1539</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>025_jpg.rf.f06a8c53e7f4b681c9427183b37f5bc2.jpg</t>
+          <t>025_jpg.rf.53dce8c7583912dd1ab113e906cf36fb.jpg</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C26" t="n">
-        <v>361.8809</v>
-      </c>
-      <c r="D26" t="n">
-        <v>193.003</v>
-      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2679,80 +2613,79 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.837</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J26" t="n">
-        <v>0.201</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-14.03</v>
+        <v>0.193</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.53</v>
+        <v>0.744</v>
       </c>
       <c r="M26" t="n">
-        <v>0.744</v>
-      </c>
-      <c r="N26" t="n">
-        <v>361.8809</v>
-      </c>
-      <c r="O26" t="n">
-        <v>377.8847</v>
+        <v>31</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P26" t="n">
-        <v>193.003</v>
+        <v>1.104</v>
       </c>
       <c r="Q26" t="n">
-        <v>201.5384</v>
+        <v>377.8506</v>
       </c>
       <c r="R26" t="n">
-        <v>10.56</v>
+        <v>201.5202</v>
       </c>
       <c r="S26" t="n">
-        <v>9.77</v>
+        <v>70</v>
       </c>
       <c r="T26" t="n">
-        <v>6.84</v>
+        <v>37.3333</v>
       </c>
       <c r="U26" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>A點在mask外、牙形不夠細長</t>
-        </is>
+        <v>0.389</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.3979</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X26" t="n">
-        <v>379.8666</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>712.2503</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>026_jpg.rf.997b35ef0b16674048632d1fe4f74d00.jpg</t>
+          <t>026_jpg.rf.cfdf5a6895e2bd03cb6976a4b5cf835b.jpg</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C27" t="n">
-        <v>417.6989</v>
-      </c>
-      <c r="D27" t="n">
-        <v>222.7726</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2768,80 +2701,79 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.849</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J27" t="n">
-        <v>0.154</v>
+        <v>0.97</v>
       </c>
       <c r="K27" t="n">
-        <v>19.81</v>
+        <v>0.146</v>
       </c>
       <c r="L27" t="n">
-        <v>-12.62</v>
+        <v>0.732</v>
       </c>
       <c r="M27" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="N27" t="n">
-        <v>417.6826</v>
-      </c>
-      <c r="O27" t="n">
-        <v>431.7028</v>
+        <v>21</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P27" t="n">
-        <v>222.7639</v>
+        <v>2.087</v>
       </c>
       <c r="Q27" t="n">
-        <v>230.2414</v>
+        <v>431.7036</v>
       </c>
       <c r="R27" t="n">
-        <v>21.38</v>
+        <v>230.2418</v>
       </c>
       <c r="S27" t="n">
-        <v>31.61</v>
+        <v>163</v>
       </c>
       <c r="T27" t="n">
-        <v>17.16</v>
+        <v>86.9333</v>
       </c>
       <c r="U27" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>B點在mask外、牙形不夠細長、端點誤差抵銷(長度假準)</t>
-        </is>
+        <v>0.075</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.6485</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X27" t="n">
-        <v>428.9048</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>804.197</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>027_jpg.rf.bef5c4b7ae4115dbc519047689c1b85a.jpg</t>
+          <t>027_jpg.rf.ed6e0a09aff052ee7eb729d67c4ef8f1.jpg</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C28" t="n">
-        <v>379.6094</v>
-      </c>
-      <c r="D28" t="n">
-        <v>202.4582</v>
-      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2857,80 +2789,79 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>0.847</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J28" t="n">
-        <v>0.043</v>
+        <v>0.968</v>
       </c>
       <c r="K28" t="n">
-        <v>16.45</v>
+        <v>0.019</v>
       </c>
       <c r="L28" t="n">
-        <v>-8.59</v>
+        <v>0.756</v>
       </c>
       <c r="M28" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="N28" t="n">
-        <v>379.564</v>
-      </c>
-      <c r="O28" t="n">
-        <v>395.5918</v>
+        <v>11</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P28" t="n">
-        <v>202.434</v>
+        <v>2.231</v>
       </c>
       <c r="Q28" t="n">
-        <v>210.9821</v>
+        <v>395.5914</v>
       </c>
       <c r="R28" t="n">
-        <v>6.86</v>
+        <v>210.9819</v>
       </c>
       <c r="S28" t="n">
-        <v>19.93</v>
+        <v>133</v>
       </c>
       <c r="T28" t="n">
-        <v>17.69</v>
+        <v>70.9333</v>
       </c>
       <c r="U28" t="n">
-        <v>20.62</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
+        <v>0.062</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.9744</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X28" t="n">
-        <v>401.3179</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>752.4715</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>028_jpg.rf.9dc294ecb02a107d9bb666dcad46368b.jpg</t>
+          <t>028_jpg.rf.f3a5fa4f1100ce1f1b2fe62a286f4243.jpg</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C29" t="n">
-        <v>400.2391</v>
-      </c>
-      <c r="D29" t="n">
-        <v>213.4607</v>
-      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2946,80 +2877,79 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>0.894</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J29" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" t="n">
-        <v>29</v>
-      </c>
       <c r="L29" t="n">
-        <v>-17.08</v>
+        <v>0.756</v>
       </c>
       <c r="M29" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="N29" t="n">
-        <v>400.2028</v>
-      </c>
-      <c r="O29" t="n">
+        <v>21</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="Q29" t="n">
         <v>430.3728</v>
       </c>
-      <c r="P29" t="n">
-        <v>213.4414</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>229.532</v>
       </c>
-      <c r="R29" t="n">
-        <v>13.7</v>
-      </c>
       <c r="S29" t="n">
-        <v>24.22</v>
+        <v>151</v>
       </c>
       <c r="T29" t="n">
-        <v>25.34</v>
+        <v>80.5333</v>
       </c>
       <c r="U29" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>B點在mask外、端點誤差抵銷(長度假準)</t>
-        </is>
+        <v>0.113</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.8502</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X29" t="n">
-        <v>424.1853</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>795.3479</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>029_jpg.rf.68aa50dedf23782d475ba73aeefa8402.jpg</t>
+          <t>029_jpg.rf.7a37fc1012f6f1b9f3383cea6ef2e45d.jpg</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0.7960199999999999</v>
       </c>
-      <c r="C30" t="n">
-        <v>319.2519</v>
-      </c>
-      <c r="D30" t="n">
-        <v>254.1309</v>
-      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3035,80 +2965,75 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.863</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J30" t="n">
-        <v>0.078</v>
+        <v>0.971</v>
       </c>
       <c r="K30" t="n">
-        <v>20.75</v>
+        <v>0.055</v>
       </c>
       <c r="L30" t="n">
-        <v>-5.65</v>
+        <v>0.744</v>
       </c>
       <c r="M30" t="n">
-        <v>0.744</v>
-      </c>
-      <c r="N30" t="n">
-        <v>318.6635</v>
-      </c>
-      <c r="O30" t="n">
-        <v>335.8687</v>
+        <v>11</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P30" t="n">
-        <v>253.6625</v>
+        <v>1.903</v>
       </c>
       <c r="Q30" t="n">
-        <v>267.3582</v>
+        <v>335.8685</v>
       </c>
       <c r="R30" t="n">
-        <v>9.66</v>
+        <v>267.358</v>
       </c>
       <c r="S30" t="n">
-        <v>0.89</v>
+        <v>123</v>
       </c>
       <c r="T30" t="n">
-        <v>18.56</v>
+        <v>97.9105</v>
       </c>
       <c r="U30" t="n">
-        <v>11.31</v>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>牙形不夠細長</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X30" t="n">
-        <v>332.8494</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>418.142</v>
+        <v>0.162</v>
+      </c>
+      <c r="V30" t="n">
+        <v>2.7306</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>030_jpg.rf.324003241288b34853323a8b697e5754.jpg</t>
+          <t>030_jpg.rf.cbb0a79529edc5568178cf06bafeb089.jpg</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C31" t="n">
-        <v>469.1043</v>
-      </c>
-      <c r="D31" t="n">
-        <v>250.1888</v>
-      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3124,80 +3049,75 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>0.835</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J31" t="n">
-        <v>0.033</v>
+        <v>0.916</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.87</v>
+        <v>0.011</v>
       </c>
       <c r="L31" t="n">
-        <v>-33.76</v>
+        <v>0.73</v>
       </c>
       <c r="M31" t="n">
-        <v>0.729</v>
-      </c>
-      <c r="N31" t="n">
-        <v>468.4842</v>
-      </c>
-      <c r="O31" t="n">
-        <v>434.7209</v>
+        <v>21</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P31" t="n">
-        <v>249.8581</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>231.851</v>
+        <v>434.6735</v>
       </c>
       <c r="R31" t="n">
-        <v>16.63</v>
+        <v>231.8257</v>
       </c>
       <c r="S31" t="n">
-        <v>10.53</v>
+        <v>154</v>
       </c>
       <c r="T31" t="n">
-        <v>13.25</v>
+        <v>82.13330000000001</v>
       </c>
       <c r="U31" t="n">
-        <v>33.58</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>B點在mask外、牙形不夠細長</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X31" t="n">
-        <v>428.738</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>803.8843000000001</v>
+        <v>0.1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.8226</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>031_jpg.rf.81b158711b26da9baabc14f9d9de3b5a.jpg</t>
+          <t>031_jpg.rf.1ed000144fa3b11934892b9671c1e781.jpg</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C32" t="n">
-        <v>373.0809</v>
-      </c>
-      <c r="D32" t="n">
-        <v>99.4884</v>
-      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3213,80 +3133,79 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0.867</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J32" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="K32" t="n">
-        <v>44.96</v>
-      </c>
       <c r="L32" t="n">
-        <v>2.78</v>
+        <v>0.74</v>
       </c>
       <c r="M32" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N32" t="n">
-        <v>372.7862</v>
-      </c>
-      <c r="O32" t="n">
-        <v>432.0012</v>
+        <v>21</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P32" t="n">
-        <v>99.4098</v>
+        <v>2.322</v>
       </c>
       <c r="Q32" t="n">
-        <v>115.2005</v>
+        <v>432.0006</v>
       </c>
       <c r="R32" t="n">
-        <v>21.76</v>
+        <v>115.2003</v>
       </c>
       <c r="S32" t="n">
-        <v>11.85</v>
+        <v>150</v>
       </c>
       <c r="T32" t="n">
-        <v>35.21</v>
+        <v>40.0001</v>
       </c>
       <c r="U32" t="n">
-        <v>24.45</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>牙形不夠細長</t>
-        </is>
+        <v>0.091</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.88</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X32" t="n">
-        <v>425.6716</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1596.2665</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>032_jpg.rf.3d37a54c9ba12c154d2dfd85c178f1a5.jpg</t>
+          <t>032_jpg.rf.877e0e9d11cc4ff0a204e9cd3caaafd6.jpg</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C33" t="n">
-        <v>375.2209</v>
-      </c>
-      <c r="D33" t="n">
-        <v>100.059</v>
-      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3302,76 +3221,79 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>0.844</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J33" t="n">
-        <v>0.045</v>
+        <v>0.965</v>
       </c>
       <c r="K33" t="n">
-        <v>25.51</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>10.78</v>
+        <v>0.762</v>
       </c>
       <c r="M33" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="N33" t="n">
-        <v>374.9517</v>
-      </c>
-      <c r="O33" t="n">
-        <v>427.1144</v>
+        <v>11</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P33" t="n">
-        <v>99.9872</v>
+        <v>2.213</v>
       </c>
       <c r="Q33" t="n">
+        <v>427.1143</v>
+      </c>
+      <c r="R33" t="n">
         <v>113.8973</v>
       </c>
-      <c r="R33" t="n">
-        <v>12.97</v>
-      </c>
       <c r="S33" t="n">
-        <v>6.26</v>
+        <v>145</v>
       </c>
       <c r="T33" t="n">
-        <v>24.96</v>
+        <v>38.6667</v>
       </c>
       <c r="U33" t="n">
-        <v>24.52</v>
-      </c>
-      <c r="V33" t="inlineStr"/>
+        <v>0.144</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.9456</v>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X33" t="n">
-        <v>420.1548</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1575.5785</v>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>⚠️是</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>034_jpg.rf.e3e831d8a4dff6095497e0b762a559db.jpg</t>
+          <t>034_jpg.rf.d7426278556ad57f73079b35d25ef281.jpg</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C34" t="n">
-        <v>398.3814</v>
-      </c>
-      <c r="D34" t="n">
-        <v>106.2352</v>
-      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3387,80 +3309,79 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0.829</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J34" t="n">
-        <v>0.185</v>
+        <v>0.953</v>
       </c>
       <c r="K34" t="n">
-        <v>26.42</v>
+        <v>0.158</v>
       </c>
       <c r="L34" t="n">
-        <v>-12.04</v>
+        <v>0.821</v>
       </c>
       <c r="M34" t="n">
-        <v>0.821</v>
-      </c>
-      <c r="N34" t="n">
-        <v>398.2564</v>
-      </c>
-      <c r="O34" t="n">
-        <v>428.0123</v>
+        <v>22</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P34" t="n">
-        <v>106.2018</v>
+        <v>1.996</v>
       </c>
       <c r="Q34" t="n">
-        <v>114.1368</v>
+        <v>428.0106</v>
       </c>
       <c r="R34" t="n">
-        <v>21.58</v>
+        <v>114.1363</v>
       </c>
       <c r="S34" t="n">
-        <v>7.19</v>
+        <v>116</v>
       </c>
       <c r="T34" t="n">
-        <v>28.1</v>
+        <v>30.9334</v>
       </c>
       <c r="U34" t="n">
-        <v>27.38</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="V34" t="n">
+        <v>3.6897</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X34" t="n">
-        <v>429.1557</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1609.3319</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>036_jpg.rf.8c4d79098e6081cff2adacdd480d6f2f.jpg</t>
+          <t>036_jpg.rf.b3e624f1dc8935a1db79e67e87ddfadc.jpg</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C35" t="n">
-        <v>408.965</v>
-      </c>
-      <c r="D35" t="n">
-        <v>218.1145</v>
-      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3476,80 +3397,79 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.775</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J35" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="n">
-        <v>-7.95</v>
-      </c>
       <c r="L35" t="n">
-        <v>-31.66</v>
+        <v>0.782</v>
       </c>
       <c r="M35" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="N35" t="n">
-        <v>408.3019</v>
-      </c>
-      <c r="O35" t="n">
-        <v>376.8319</v>
+        <v>12</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P35" t="n">
-        <v>217.7609</v>
+        <v>1.458</v>
       </c>
       <c r="Q35" t="n">
-        <v>200.9769</v>
+        <v>376.8315</v>
       </c>
       <c r="R35" t="n">
-        <v>21.55</v>
+        <v>200.9766</v>
       </c>
       <c r="S35" t="n">
-        <v>11.52</v>
+        <v>108</v>
       </c>
       <c r="T35" t="n">
-        <v>15.95</v>
+        <v>57.6</v>
       </c>
       <c r="U35" t="n">
-        <v>23.88</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
+        <v>0.089</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3.4892</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
+          <t>兩法選到不同mask、冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X35" t="n">
-        <v>374.8872</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>702.9139</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>037_jpg.rf.819921ec8736ee833b89865b2a32b82c.jpg</t>
+          <t>037_jpg.rf.a64a1a57aaa5a4d4b54a3780a8ce0073.jpg</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C36" t="n">
-        <v>343.9882</v>
-      </c>
-      <c r="D36" t="n">
-        <v>183.4603</v>
-      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3565,80 +3485,75 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>0.889</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J36" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="n">
-        <v>28.86</v>
-      </c>
       <c r="L36" t="n">
-        <v>-10.81</v>
+        <v>0.755</v>
       </c>
       <c r="M36" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="N36" t="n">
-        <v>342.932</v>
-      </c>
-      <c r="O36" t="n">
-        <v>394.5152</v>
+        <v>21</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P36" t="n">
-        <v>182.8969</v>
+        <v>2.357</v>
       </c>
       <c r="Q36" t="n">
-        <v>210.408</v>
+        <v>394.5163</v>
       </c>
       <c r="R36" t="n">
-        <v>30.39</v>
+        <v>210.4085</v>
       </c>
       <c r="S36" t="n">
-        <v>24.22</v>
+        <v>148</v>
       </c>
       <c r="T36" t="n">
-        <v>24.18</v>
+        <v>78.9333</v>
       </c>
       <c r="U36" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>B點在mask外、端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X36" t="n">
-        <v>384.4683</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>720.8785</v>
+        <v>0.126</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.6657</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>038_jpg.rf.1a136bcdeab9ab0647ca0144bcfec321.jpg</t>
+          <t>038_jpg.rf.c4be0456da6e8262ed040a60b1cc3541.jpg</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C37" t="n">
-        <v>282.1442</v>
-      </c>
-      <c r="D37" t="n">
-        <v>150.4768</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3654,80 +3569,75 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.756</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J37" t="n">
-        <v>0.119</v>
+        <v>0.911</v>
       </c>
       <c r="K37" t="n">
-        <v>25.88</v>
+        <v>0.066</v>
       </c>
       <c r="L37" t="n">
-        <v>-42.27</v>
+        <v>0.725</v>
       </c>
       <c r="M37" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="N37" t="n">
-        <v>276.5067</v>
-      </c>
-      <c r="O37" t="n">
-        <v>368.3058</v>
+        <v>22</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P37" t="n">
-        <v>147.4702</v>
+        <v>2.044</v>
       </c>
       <c r="Q37" t="n">
-        <v>196.4297</v>
+        <v>368.3077</v>
       </c>
       <c r="R37" t="n">
-        <v>11.17</v>
+        <v>196.4307</v>
       </c>
       <c r="S37" t="n">
-        <v>49.46</v>
+        <v>121</v>
       </c>
       <c r="T37" t="n">
-        <v>27.66</v>
+        <v>64.5333</v>
       </c>
       <c r="U37" t="n">
-        <v>121.99</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>B點在mask外、牙形不夠細長</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X37" t="n">
-        <v>375.1675</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>703.4395</v>
+        <v>0.203</v>
+      </c>
+      <c r="V37" t="n">
+        <v>3.0439</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>039_jpg.rf.8aa0b7f7f99062b04dfaa93d6a8b3eb8.jpg</t>
+          <t>039_jpg.rf.9e9a050d1df53938e102f241a800ad16.jpg</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C38" t="n">
-        <v>466.4733</v>
-      </c>
-      <c r="D38" t="n">
-        <v>248.7856</v>
-      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3743,80 +3653,79 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>0.6889999999999999</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J38" t="n">
-        <v>0.119</v>
+        <v>0.827</v>
       </c>
       <c r="K38" t="n">
-        <v>9.609999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="L38" t="n">
-        <v>-18.58</v>
+        <v>0.763</v>
       </c>
       <c r="M38" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="N38" t="n">
-        <v>465.4346</v>
-      </c>
-      <c r="O38" t="n">
-        <v>461.7809</v>
+        <v>11</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P38" t="n">
-        <v>248.2317</v>
+        <v>1.85</v>
       </c>
       <c r="Q38" t="n">
-        <v>246.283</v>
+        <v>461.7791</v>
       </c>
       <c r="R38" t="n">
-        <v>13.3</v>
+        <v>246.2821</v>
       </c>
       <c r="S38" t="n">
-        <v>70.45</v>
+        <v>153</v>
       </c>
       <c r="T38" t="n">
-        <v>12.63</v>
+        <v>81.59990000000001</v>
       </c>
       <c r="U38" t="n">
-        <v>48.35</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="V38" t="n">
+        <v>3.0182</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X38" t="n">
-        <v>522.614</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>979.9019</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>040_jpg.rf.df5a982adce80e1535fd79f09915d73e.jpg</t>
+          <t>040_jpg.rf.3deb2c457e4b0ef9a2dc1b8a45667489.jpg</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C39" t="n">
-        <v>408.1203</v>
-      </c>
-      <c r="D39" t="n">
-        <v>217.664</v>
-      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3832,80 +3741,79 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>0.85</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J39" t="n">
-        <v>0.052</v>
+        <v>0.926</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.63</v>
+        <v>0.004</v>
       </c>
       <c r="L39" t="n">
-        <v>-21.33</v>
+        <v>0.711</v>
       </c>
       <c r="M39" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="N39" t="n">
-        <v>405.8366</v>
-      </c>
-      <c r="O39" t="n">
-        <v>374.7034</v>
+        <v>21</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P39" t="n">
-        <v>216.4461</v>
+        <v>2.214</v>
       </c>
       <c r="Q39" t="n">
-        <v>199.8417</v>
+        <v>374.7038</v>
       </c>
       <c r="R39" t="n">
-        <v>2.49</v>
+        <v>199.8419</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="T39" t="n">
-        <v>37.38</v>
+        <v>85.86660000000001</v>
       </c>
       <c r="U39" t="n">
-        <v>18.34</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>A點在mask外、B點在mask外、牙形不夠細長</t>
-        </is>
+        <v>0.065</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.3274</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X39" t="n">
-        <v>376.6634</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>706.2443</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>041_jpg.rf.8deb0897ced5e98b0632a5bd5c8aa066.jpg</t>
+          <t>041_jpg.rf.4bbbfea36253186251bba070ece9e7c7.jpg</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C40" t="n">
-        <v>447.2093</v>
-      </c>
-      <c r="D40" t="n">
-        <v>238.5115</v>
-      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3921,80 +3829,79 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>0.872</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J40" t="n">
-        <v>0.121</v>
+        <v>0.916</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.45</v>
+        <v>0.101</v>
       </c>
       <c r="L40" t="n">
-        <v>-15.69</v>
+        <v>0.755</v>
       </c>
       <c r="M40" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="N40" t="n">
-        <v>447.1834</v>
-      </c>
-      <c r="O40" t="n">
-        <v>436.4576</v>
+        <v>21</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P40" t="n">
-        <v>238.4977</v>
+        <v>2.193</v>
       </c>
       <c r="Q40" t="n">
-        <v>232.7772</v>
+        <v>436.4457</v>
       </c>
       <c r="R40" t="n">
-        <v>9.800000000000001</v>
+        <v>232.7709</v>
       </c>
       <c r="S40" t="n">
-        <v>15.96</v>
+        <v>151</v>
       </c>
       <c r="T40" t="n">
-        <v>6.97</v>
+        <v>80.5333</v>
       </c>
       <c r="U40" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
+        <v>0.054</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2.8904</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X40" t="n">
-        <v>437.7244</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>820.7338</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>042_jpg.rf.537450cea4fdf0981f62c887cde69683.jpg</t>
+          <t>042_jpg.rf.b5d22e7fba96fff8e1bc826bf0ec0937.jpg</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0.347448</v>
       </c>
-      <c r="C41" t="n">
-        <v>413.6572</v>
-      </c>
-      <c r="D41" t="n">
-        <v>143.7244</v>
-      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4010,76 +3917,79 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>0.828</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J41" t="n">
-        <v>0.003</v>
+        <v>0.923</v>
       </c>
       <c r="K41" t="n">
-        <v>32.61</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>14.06</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="N41" t="n">
-        <v>413.3547</v>
-      </c>
-      <c r="O41" t="n">
-        <v>467.8704</v>
+        <v>22</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P41" t="n">
-        <v>143.6193</v>
+        <v>1.779</v>
       </c>
       <c r="Q41" t="n">
-        <v>162.5606</v>
+        <v>467.8099</v>
       </c>
       <c r="R41" t="n">
-        <v>8.5</v>
+        <v>162.5396</v>
       </c>
       <c r="S41" t="n">
-        <v>18.89</v>
+        <v>126</v>
       </c>
       <c r="T41" t="n">
-        <v>31.45</v>
+        <v>43.7784</v>
       </c>
       <c r="U41" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="V41" t="inlineStr"/>
+        <v>0.136</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3.7128</v>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X41" t="n">
-        <v>477.2216</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1373.5051</v>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>⚠️是</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>043_jpg.rf.1cfa29c51078c1490e4f53e0dbe550d0.jpg</t>
+          <t>043_jpg.rf.0335132c4f94a47f07539e86712ae9e6.jpg</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C42" t="n">
-        <v>425.6231</v>
-      </c>
-      <c r="D42" t="n">
-        <v>226.9989</v>
-      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4095,80 +4005,75 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>0.855</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J42" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="K42" t="n">
-        <v>11.71</v>
-      </c>
       <c r="L42" t="n">
-        <v>-19.9</v>
+        <v>0.783</v>
       </c>
       <c r="M42" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="N42" t="n">
-        <v>425.6145</v>
-      </c>
-      <c r="O42" t="n">
-        <v>421.9677</v>
+        <v>12</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P42" t="n">
-        <v>226.9943</v>
+        <v>2.033</v>
       </c>
       <c r="Q42" t="n">
-        <v>225.0493</v>
+        <v>421.9668</v>
       </c>
       <c r="R42" t="n">
-        <v>16.02</v>
+        <v>225.0488</v>
       </c>
       <c r="S42" t="n">
-        <v>22.22</v>
+        <v>136</v>
       </c>
       <c r="T42" t="n">
-        <v>8.23</v>
+        <v>72.5333</v>
       </c>
       <c r="U42" t="n">
-        <v>29.33</v>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>B點在mask外</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X42" t="n">
-        <v>407.7123</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>764.461</v>
+        <v>0.134</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3.1027</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>044_jpg.rf.51542370502344e22d3b7f6d7fc12612.jpg</t>
+          <t>044_jpg.rf.b6e79f35ae21127d7114b91bee408d7d.jpg</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0.811153</v>
       </c>
-      <c r="C43" t="n">
-        <v>328.3778</v>
-      </c>
-      <c r="D43" t="n">
-        <v>266.3647</v>
-      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4184,76 +4089,79 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>0.732</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J43" t="n">
-        <v>0.074</v>
+        <v>0.9</v>
       </c>
       <c r="K43" t="n">
-        <v>0.47</v>
+        <v>0.05</v>
       </c>
       <c r="L43" t="n">
-        <v>-7.42</v>
+        <v>0.819</v>
       </c>
       <c r="M43" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="N43" t="n">
-        <v>327.0747</v>
-      </c>
-      <c r="O43" t="n">
-        <v>326.0755</v>
+        <v>31</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P43" t="n">
-        <v>265.3076</v>
+        <v>1.977</v>
       </c>
       <c r="Q43" t="n">
-        <v>264.4971</v>
+        <v>325.96</v>
       </c>
       <c r="R43" t="n">
-        <v>30.57</v>
+        <v>264.4034</v>
       </c>
       <c r="S43" t="n">
-        <v>7.34</v>
+        <v>85</v>
       </c>
       <c r="T43" t="n">
-        <v>7.82</v>
+        <v>68.94799999999999</v>
       </c>
       <c r="U43" t="n">
-        <v>15.72</v>
-      </c>
-      <c r="V43" t="inlineStr"/>
+        <v>0.054</v>
+      </c>
+      <c r="V43" t="n">
+        <v>3.8348</v>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X43" t="n">
-        <v>329.8247</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>406.6122</v>
+          <t>兩法選到不同mask、冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>⚠️是</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>045_jpg.rf.e46cb1980f7a6958622ed2ded4ffffac.jpg</t>
+          <t>045_jpg.rf.f7b24cdaf9c17654e7cf9e869b4757cd.jpg</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C44" t="n">
-        <v>381.1884</v>
-      </c>
-      <c r="D44" t="n">
-        <v>203.3004</v>
-      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4269,80 +4177,79 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>0.83</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J44" t="n">
-        <v>0.161</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-12.04</v>
+        <v>0.148</v>
       </c>
       <c r="L44" t="n">
-        <v>-6.35</v>
+        <v>0.789</v>
       </c>
       <c r="M44" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="N44" t="n">
-        <v>379.5536</v>
-      </c>
-      <c r="O44" t="n">
-        <v>368.7074</v>
+        <v>32</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P44" t="n">
-        <v>202.4285</v>
+        <v>2.065</v>
       </c>
       <c r="Q44" t="n">
-        <v>196.6438</v>
+        <v>368.6988</v>
       </c>
       <c r="R44" t="n">
-        <v>4.74</v>
+        <v>196.6392</v>
       </c>
       <c r="S44" t="n">
-        <v>23.84</v>
+        <v>103</v>
       </c>
       <c r="T44" t="n">
-        <v>11.17</v>
+        <v>54.9333</v>
       </c>
       <c r="U44" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>A點在mask外</t>
-        </is>
+        <v>0.14</v>
+      </c>
+      <c r="V44" t="n">
+        <v>3.5796</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X44" t="n">
-        <v>366.1772</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>686.5827</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>046_jpg.rf.0ca1b25cce4f59cd52ca2becb31fd347.jpg</t>
+          <t>046_jpg.rf.76f88b64402215cc443ed5cde0e097f2.jpg</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C45" t="n">
-        <v>391.9829</v>
-      </c>
-      <c r="D45" t="n">
-        <v>209.0574</v>
-      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4358,80 +4265,75 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>0.694</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J45" t="n">
-        <v>0.151</v>
+        <v>0.965</v>
       </c>
       <c r="K45" t="n">
-        <v>3.18</v>
+        <v>0.147</v>
       </c>
       <c r="L45" t="n">
-        <v>9.57</v>
+        <v>0.801</v>
       </c>
       <c r="M45" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="N45" t="n">
-        <v>391.8822</v>
-      </c>
-      <c r="O45" t="n">
-        <v>413.9825</v>
+        <v>41</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P45" t="n">
-        <v>209.0037</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>220.7906</v>
+        <v>413.9808</v>
       </c>
       <c r="R45" t="n">
-        <v>12.49</v>
+        <v>220.7896</v>
       </c>
       <c r="S45" t="n">
-        <v>18.12</v>
+        <v>98</v>
       </c>
       <c r="T45" t="n">
-        <v>4.16</v>
+        <v>52.2666</v>
       </c>
       <c r="U45" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X45" t="n">
-        <v>412.5052</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>773.4477000000001</v>
+        <v>0.103</v>
+      </c>
+      <c r="V45" t="n">
+        <v>4.2243</v>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>047_jpg.rf.3e39cddbb127fc0627c898159bd295c5.jpg</t>
+          <t>047_jpg.rf.6a632fd4b65280f5d73a840a623469ea.jpg</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0.5333329999999999</v>
       </c>
-      <c r="C46" t="n">
-        <v>337.8765</v>
-      </c>
-      <c r="D46" t="n">
-        <v>180.2007</v>
-      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4447,80 +4349,79 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>0.904</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J46" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K46" t="n">
         <v>0</v>
       </c>
-      <c r="K46" t="n">
-        <v>29</v>
-      </c>
       <c r="L46" t="n">
-        <v>-1.23</v>
+        <v>0.698</v>
       </c>
       <c r="M46" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="N46" t="n">
-        <v>337.4223</v>
-      </c>
-      <c r="O46" t="n">
-        <v>379.2525</v>
+        <v>11</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P46" t="n">
-        <v>179.9585</v>
+        <v>2.166</v>
       </c>
       <c r="Q46" t="n">
-        <v>202.2679</v>
+        <v>379.2561</v>
       </c>
       <c r="R46" t="n">
-        <v>24.19</v>
+        <v>202.2698</v>
       </c>
       <c r="S46" t="n">
-        <v>6.02</v>
+        <v>164</v>
       </c>
       <c r="T46" t="n">
-        <v>34.43</v>
+        <v>87.4666</v>
       </c>
       <c r="U46" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="V46" t="inlineStr">
+        <v>0.179</v>
+      </c>
+      <c r="V46" t="n">
+        <v>2.3125</v>
+      </c>
+      <c r="W46" t="inlineStr">
         <is>
           <t>牙形不夠細長</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X46" t="n">
-        <v>374.2398</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>701.7001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>048_jpg.rf.d2a9efb5a7dd6aa7a3c68edf3e1964fa.jpg</t>
+          <t>048_jpg.rf.bf3293ace23a9a7192c3fd3f36901326.jpg</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C47" t="n">
-        <v>436.0364</v>
-      </c>
-      <c r="D47" t="n">
-        <v>116.2765</v>
-      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4536,80 +4437,79 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>0.857</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J47" t="n">
-        <v>0.022</v>
+        <v>0.959</v>
       </c>
       <c r="K47" t="n">
-        <v>26.51</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>-10.65</v>
+        <v>0.742</v>
       </c>
       <c r="M47" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="N47" t="n">
-        <v>435.4925</v>
-      </c>
-      <c r="O47" t="n">
-        <v>458.231</v>
+        <v>11</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P47" t="n">
-        <v>116.1315</v>
+        <v>2.031</v>
       </c>
       <c r="Q47" t="n">
-        <v>122.1951</v>
+        <v>458.1702</v>
       </c>
       <c r="R47" t="n">
-        <v>17.64</v>
+        <v>122.1789</v>
       </c>
       <c r="S47" t="n">
-        <v>15.98</v>
+        <v>172</v>
       </c>
       <c r="T47" t="n">
-        <v>33.78</v>
+        <v>45.8667</v>
       </c>
       <c r="U47" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>B點在mask外、牙形不夠細長、端點誤差抵銷(長度假準)</t>
-        </is>
+        <v>0.159</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2.6638</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X47" t="n">
-        <v>465.8273</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1746.8502</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>049_jpg.rf.b141f7e16aacaaeb3d29fbdccdd4fe3e.jpg</t>
+          <t>049_jpg.rf.7897e5c4b008ac17dda52677eb16b205.jpg</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C48" t="n">
-        <v>373.5495</v>
-      </c>
-      <c r="D48" t="n">
-        <v>99.6133</v>
-      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4625,80 +4525,79 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.855</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J48" t="n">
-        <v>0.03</v>
+        <v>0.894</v>
       </c>
       <c r="K48" t="n">
-        <v>26.16</v>
+        <v>0.029</v>
       </c>
       <c r="L48" t="n">
-        <v>16.86</v>
+        <v>0.719</v>
       </c>
       <c r="M48" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="N48" t="n">
-        <v>372.6972</v>
-      </c>
-      <c r="O48" t="n">
-        <v>423.0235</v>
+        <v>21</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P48" t="n">
-        <v>99.386</v>
+        <v>2.116</v>
       </c>
       <c r="Q48" t="n">
-        <v>112.8064</v>
+        <v>424.0402</v>
       </c>
       <c r="R48" t="n">
-        <v>13.9</v>
+        <v>113.0775</v>
       </c>
       <c r="S48" t="n">
-        <v>34.03</v>
+        <v>172</v>
       </c>
       <c r="T48" t="n">
-        <v>18.52</v>
+        <v>45.8667</v>
       </c>
       <c r="U48" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>牙形不夠細長</t>
-        </is>
+        <v>0.112</v>
+      </c>
+      <c r="V48" t="n">
+        <v>2.4653</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X48" t="n">
-        <v>437.7673</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1641.6253</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>050_jpg.rf.c8c57a2d704b2ddbe1e8b0d476f7c4d2.jpg</t>
+          <t>050_jpg.rf.4958636e3e2fe16c23221882cbfdb04d.jpg</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C49" t="n">
-        <v>410.6174</v>
-      </c>
-      <c r="D49" t="n">
-        <v>109.4981</v>
-      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4714,80 +4613,75 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0.763</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J49" t="n">
-        <v>0.039</v>
+        <v>0.894</v>
       </c>
       <c r="K49" t="n">
-        <v>7.53</v>
+        <v>0.013</v>
       </c>
       <c r="L49" t="n">
-        <v>13.93</v>
+        <v>0.785</v>
       </c>
       <c r="M49" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="N49" t="n">
-        <v>410.176</v>
-      </c>
-      <c r="O49" t="n">
-        <v>441.8783</v>
+        <v>22</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P49" t="n">
-        <v>109.3804</v>
+        <v>1.798</v>
       </c>
       <c r="Q49" t="n">
-        <v>117.8344</v>
+        <v>441.886</v>
       </c>
       <c r="R49" t="n">
-        <v>21.17</v>
+        <v>117.8364</v>
       </c>
       <c r="S49" t="n">
-        <v>12.64</v>
+        <v>129</v>
       </c>
       <c r="T49" t="n">
-        <v>13.82</v>
+        <v>34.4</v>
       </c>
       <c r="U49" t="n">
-        <v>29.81</v>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X49" t="n">
-        <v>451.5336</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1693.2489</v>
+        <v>0.219</v>
+      </c>
+      <c r="V49" t="n">
+        <v>3.4255</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>051_jpg.rf.ee071fb1b0f034836f5eb0deae7cb200.jpg</t>
+          <t>051_jpg.rf.118bab4a6988aee4201a5fea725f651f.jpg</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C50" t="n">
-        <v>397.1215</v>
-      </c>
-      <c r="D50" t="n">
-        <v>105.8992</v>
-      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4803,80 +4697,79 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>0.876</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J50" t="n">
-        <v>0.025</v>
+        <v>0.947</v>
       </c>
       <c r="K50" t="n">
-        <v>23.41</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>-12.84</v>
+        <v>0.745</v>
       </c>
       <c r="M50" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="N50" t="n">
-        <v>396.4051</v>
-      </c>
-      <c r="O50" t="n">
-        <v>420.6251</v>
+        <v>11</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P50" t="n">
-        <v>105.7082</v>
+        <v>1.773</v>
       </c>
       <c r="Q50" t="n">
-        <v>112.1668</v>
+        <v>420.6257</v>
       </c>
       <c r="R50" t="n">
-        <v>8.859999999999999</v>
+        <v>112.167</v>
       </c>
       <c r="S50" t="n">
-        <v>6.24</v>
+        <v>155</v>
       </c>
       <c r="T50" t="n">
-        <v>22.44</v>
+        <v>41.3334</v>
       </c>
       <c r="U50" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>B點在mask外、牙形不夠細長</t>
-        </is>
+        <v>0.163</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2.7137</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X50" t="n">
-        <v>414.0762</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1552.7838</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>052_jpg.rf.05513e55c358a01918e86390d9e777b0.jpg</t>
+          <t>052_jpg.rf.e73b115cdceaf7c86dad1611452102c0.jpg</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C51" t="n">
-        <v>409.9502</v>
-      </c>
-      <c r="D51" t="n">
-        <v>109.3202</v>
-      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4892,80 +4785,75 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.819</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J51" t="n">
-        <v>0.006</v>
+        <v>0.923</v>
       </c>
       <c r="K51" t="n">
-        <v>28.35</v>
+        <v>0.011</v>
       </c>
       <c r="L51" t="n">
-        <v>-11.01</v>
+        <v>0.747</v>
       </c>
       <c r="M51" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="N51" t="n">
-        <v>408.652</v>
-      </c>
-      <c r="O51" t="n">
-        <v>427.5732</v>
+        <v>21</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>牙位(上顎冠朝下)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P51" t="n">
-        <v>108.974</v>
+        <v>1.751</v>
       </c>
       <c r="Q51" t="n">
-        <v>114.0197</v>
+        <v>427.0673</v>
       </c>
       <c r="R51" t="n">
-        <v>8.49</v>
+        <v>113.8848</v>
       </c>
       <c r="S51" t="n">
-        <v>37.54</v>
+        <v>152</v>
       </c>
       <c r="T51" t="n">
-        <v>25.43</v>
+        <v>40.5334</v>
       </c>
       <c r="U51" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>B點在mask外、牙形不夠細長</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X51" t="n">
-        <v>424.2968</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1591.111</v>
+        <v>0.118</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2.8097</v>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>054_jpg.rf.7a41f58896616b25f092f23715df71aa.jpg</t>
+          <t>054_jpg.rf.1120f4cec7153f33539442a19696cbc3.jpg</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C52" t="n">
-        <v>393.9528</v>
-      </c>
-      <c r="D52" t="n">
-        <v>105.0542</v>
-      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>✅</t>
@@ -4981,80 +4869,79 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>0.853</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J52" t="n">
-        <v>0.164</v>
+        <v>0.95</v>
       </c>
       <c r="K52" t="n">
-        <v>-11.3</v>
+        <v>0.135</v>
       </c>
       <c r="L52" t="n">
-        <v>4.42</v>
+        <v>0.761</v>
       </c>
       <c r="M52" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="N52" t="n">
-        <v>392.9689</v>
-      </c>
-      <c r="O52" t="n">
-        <v>396.3121</v>
+        <v>32</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P52" t="n">
-        <v>104.7918</v>
+        <v>1.884</v>
       </c>
       <c r="Q52" t="n">
-        <v>105.6834</v>
+        <v>396.3118</v>
       </c>
       <c r="R52" t="n">
-        <v>11.79</v>
+        <v>105.6833</v>
       </c>
       <c r="S52" t="n">
-        <v>32.87</v>
+        <v>116</v>
       </c>
       <c r="T52" t="n">
-        <v>13.49</v>
+        <v>30.9334</v>
       </c>
       <c r="U52" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>A點在mask外</t>
-        </is>
+        <v>0.11</v>
+      </c>
+      <c r="V52" t="n">
+        <v>3.4165</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X52" t="n">
-        <v>397.6199</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1491.0728</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>055_jpg.rf.5978dcb08ec19062a87cfe4b44173ecb.jpg</t>
+          <t>055_jpg.rf.9403ef7ae724ecc778852c7968e2eb87.jpg</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C53" t="n">
-        <v>364.5693</v>
-      </c>
-      <c r="D53" t="n">
-        <v>97.2186</v>
-      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>✅</t>
@@ -5070,80 +4957,75 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0.859</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="J53" t="n">
-        <v>0.169</v>
+        <v>0.925</v>
       </c>
       <c r="K53" t="n">
-        <v>-9.02</v>
+        <v>0.163</v>
       </c>
       <c r="L53" t="n">
-        <v>-5.01</v>
+        <v>0.804</v>
       </c>
       <c r="M53" t="n">
-        <v>0.804</v>
-      </c>
-      <c r="N53" t="n">
-        <v>362.8798</v>
-      </c>
-      <c r="O53" t="n">
-        <v>363.291</v>
+        <v>31</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P53" t="n">
-        <v>96.7681</v>
+        <v>2.105</v>
       </c>
       <c r="Q53" t="n">
-        <v>96.8777</v>
+        <v>363.2894</v>
       </c>
       <c r="R53" t="n">
-        <v>14.95</v>
+        <v>96.87730000000001</v>
       </c>
       <c r="S53" t="n">
-        <v>19.69</v>
+        <v>101</v>
       </c>
       <c r="T53" t="n">
-        <v>12.91</v>
+        <v>26.9334</v>
       </c>
       <c r="U53" t="n">
-        <v>22.88</v>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>A點在mask外、端點誤差抵銷(長度假準)</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>⚠️是</t>
-        </is>
-      </c>
-      <c r="X53" t="n">
-        <v>363.2695</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1362.2589</v>
+        <v>0.109</v>
+      </c>
+      <c r="V53" t="n">
+        <v>3.5969</v>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>056_jpg.rf.4cbb6e7aac1cddedc033a5d10d3dfbe4.jpg</t>
+          <t>056_jpg.rf.7fa989e1d469f5c2b2619b20bb44876f.jpg</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C54" t="n">
-        <v>360.2853</v>
-      </c>
-      <c r="D54" t="n">
-        <v>96.0762</v>
-      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>✅</t>
@@ -5159,76 +5041,79 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.799</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J54" t="n">
-        <v>0.097</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-7.91</v>
+        <v>0.111</v>
       </c>
       <c r="L54" t="n">
-        <v>6.17</v>
+        <v>0.806</v>
       </c>
       <c r="M54" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="N54" t="n">
-        <v>359.3804</v>
-      </c>
-      <c r="O54" t="n">
+        <v>41</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="Q54" t="n">
         <v>372.3942</v>
       </c>
-      <c r="P54" t="n">
-        <v>95.8349</v>
-      </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>99.3052</v>
       </c>
-      <c r="R54" t="n">
-        <v>6.62</v>
-      </c>
       <c r="S54" t="n">
-        <v>10.45</v>
+        <v>101</v>
       </c>
       <c r="T54" t="n">
-        <v>13</v>
+        <v>26.9334</v>
       </c>
       <c r="U54" t="n">
-        <v>23.54</v>
-      </c>
-      <c r="V54" t="inlineStr"/>
+        <v>0.093</v>
+      </c>
+      <c r="V54" t="n">
+        <v>3.6871</v>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="X54" t="n">
-        <v>371.3078</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1392.4025</v>
+          <t>兩法選到不同mask、冠寬位置異常</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>⚠️是</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>057_jpg.rf.9ccaefd02e6cc640a3cd843e59908319.jpg</t>
+          <t>057_jpg.rf.6317f9fbb5ade3115ac57c42351159ae.jpg</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0.266667</v>
       </c>
-      <c r="C55" t="n">
-        <v>336.412</v>
-      </c>
-      <c r="D55" t="n">
-        <v>89.70999999999999</v>
-      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>✅</t>
@@ -5244,63 +5129,66 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0.8</v>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>⚠️否</t>
+        </is>
       </c>
       <c r="J55" t="n">
-        <v>0.185</v>
+        <v>0.949</v>
       </c>
       <c r="K55" t="n">
-        <v>11.17</v>
+        <v>0.167</v>
       </c>
       <c r="L55" t="n">
-        <v>4.22</v>
+        <v>0.765</v>
       </c>
       <c r="M55" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="N55" t="n">
-        <v>336.3007</v>
-      </c>
-      <c r="O55" t="n">
-        <v>355.7367</v>
+        <v>42</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>牙位(下顎冠朝上)</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
       <c r="P55" t="n">
-        <v>89.6803</v>
+        <v>2.13</v>
       </c>
       <c r="Q55" t="n">
-        <v>94.86320000000001</v>
+        <v>355.7368</v>
       </c>
       <c r="R55" t="n">
-        <v>18.62</v>
+        <v>94.8633</v>
       </c>
       <c r="S55" t="n">
-        <v>19.06</v>
+        <v>121</v>
       </c>
       <c r="T55" t="n">
-        <v>8.82</v>
+        <v>32.2667</v>
       </c>
       <c r="U55" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>端點誤差抵銷(長度假準)</t>
-        </is>
+        <v>0.117</v>
+      </c>
+      <c r="V55" t="n">
+        <v>2.94</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
+          <t>兩法選到不同mask</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
           <t>⚠️是</t>
         </is>
-      </c>
-      <c r="X55" t="n">
-        <v>351.3148</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1317.4289</v>
       </c>
     </row>
   </sheetData>
@@ -5314,303 +5202,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>空間</t>
+          <t>圖上顏色</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>方法</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>有效張數</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>長度MAE px</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>長度偏差(bias) px</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>誤差標準差 px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>最大絕對誤差 px</t>
+          <t>代表什麼</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>letterbox</t>
+          <t>橘黃輪廓</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>原始預測</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>54</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24.709</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-15.349</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26.804</v>
-      </c>
-      <c r="G2" t="n">
-        <v>93.023</v>
+          <t>選中的 mask(seg 預測)</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>letterbox</t>
+          <t>灰色輪廓</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>長軸投影</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>54</v>
-      </c>
-      <c r="D3" t="n">
-        <v>24.962</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-16.048</v>
-      </c>
-      <c r="F3" t="n">
-        <v>26.936</v>
-      </c>
-      <c r="G3" t="n">
-        <v>98.661</v>
+          <t>其他候選 mask，未被選中</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>letterbox</t>
+          <t>藍線 A-B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mask幾何</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>54</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6.557</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1.157</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10.777</v>
-      </c>
-      <c r="G4" t="n">
-        <v>60.833</v>
+          <t>mask 幾何長度(A=判定的切端、B=根尖端)</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>原圖</t>
+          <t>白線</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>原始預測</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>54</v>
-      </c>
-      <c r="D5" t="n">
-        <v>771.228</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-771.228</v>
-      </c>
-      <c r="F5" t="n">
-        <v>455.804</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1638.752</v>
+          <t>冠寬 ← 檢查有沒有黏到鄰牙</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>原圖</t>
+          <t>洋紅空心圈</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>長軸投影</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>54</v>
-      </c>
-      <c r="D6" t="n">
-        <v>771.567</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-771.567</v>
-      </c>
-      <c r="F6" t="n">
-        <v>455.691</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1638.782</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>原圖</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>mask幾何</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>54</v>
-      </c>
-      <c r="D7" t="n">
-        <v>765.292</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-765.292</v>
-      </c>
-      <c r="F7" t="n">
-        <v>455.443</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1633.592</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>圖上顏色</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>代表什麼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>橘黃輪廓</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>選中的 mask(seg 預測)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>灰色輪廓</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>其他候選 mask，未被選中</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>藍線 geo1-geo2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>方法3 mask幾何 ← 目前打算餵給 C1 的</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>青色虛線</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>方法2 長軸投影(預測點投影到 mask 主軸)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>綠線 A-B / 紅點B</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>方法1 原始預測(B2 現在在用的)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>洋紅空心圈</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GT 人工標註的 A/B 真值</t>
+          <t>GT 人工標註的 A/B(僅 pose 格式標註有)</t>
         </is>
       </c>
     </row>
